--- a/etf_holdings/2026-10-06_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-10-06_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2575</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.53%1325</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.53%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1325</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+9.93%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>5700</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+4.34%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>5165</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+4.22%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3585</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+5.96%7205</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+5.96%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7205</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0%626</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>626</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+6.37%2005</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+6.37%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>2005</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+3.95%5520</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+3.95%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>5520</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+2.4%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1495</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.6%2075</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.6%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>2075</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.57%152.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.57%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>152.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+9.88%1780</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+9.88%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1780</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.17%2485</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.17%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2485</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.12%2150</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.12%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2150</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3599,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3660,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3721,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3782,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3843,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3904,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3965,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +4026,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4087,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4148,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4209,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4270,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4331,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4392,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4453,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4514,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4575,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4636,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4697,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4758,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4819,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4880,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4941,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +5002,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5063,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5124,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5185,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5246,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5307,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5368,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5429,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5490,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5551,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5612,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5673,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5734,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5795,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5856,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5917,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5978,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6039,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6100,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6161,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6222,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6283,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6344,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:40</t>
+          <t>2026-10-06 02:27:17</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6405,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:40</t>
+          <t>2026-10-06 02:27:17</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6466,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:40</t>
+          <t>2026-10-06 02:27:17</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6527,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:40</t>
+          <t>2026-10-06 02:27:17</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6588,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:40</t>
+          <t>2026-10-06 02:27:17</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6649,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6710,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6771,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6832,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6893,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6954,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +7015,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7076,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7137,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7198,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7259,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7320,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7381,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7442,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7503,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7564,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7625,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7686,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7747,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7808,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7869,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7930,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7991,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8052,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8113,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8174,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8235,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8296,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8357,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8418,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8479,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8540,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8601,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8662,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8723,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8784,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8845,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8906,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8967,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +9028,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9089,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9150,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9211,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9272,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9333,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9394,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:50</t>
+          <t>2026-10-06 02:27:27</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9455,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:50</t>
+          <t>2026-10-06 02:27:27</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9516,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:50</t>
+          <t>2026-10-06 02:27:27</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9577,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:50</t>
+          <t>2026-10-06 02:27:27</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9638,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:50</t>
+          <t>2026-10-06 02:27:27</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9699,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9760,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9821,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9882,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9943,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +10004,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10065,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10126,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10187,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10248,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10309,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10370,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10431,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10492,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10553,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10614,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10675,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10736,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10797,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10858,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10919,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10980,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11041,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11102,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11163,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11224,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11285,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11346,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11407,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11468,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11529,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11590,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11651,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11712,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11773,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11834,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11895,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11956,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +12017,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12078,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12139,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12200,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12261,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12322,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12383,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12444,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12505,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12566,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12627,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12688,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12749,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12810,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12871,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12932,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12993,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13054,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13115,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13176,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13237,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13298,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13359,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13420,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13481,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13542,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13603,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13664,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13725,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13847,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13908,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13969,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14030,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:08</t>
+          <t>2026-10-06 02:27:41</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14091,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14152,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14213,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14274,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14335,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14396,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14457,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14518,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14579,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14640,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14701,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14762,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14823,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14884,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14945,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:09</t>
+          <t>2026-10-06 02:27:42</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +15006,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15067,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15128,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15189,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15250,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15311,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15372,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15433,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15494,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15555,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15616,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15677,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15738,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15799,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15860,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:10</t>
+          <t>2026-10-06 02:27:44</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15921,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:11</t>
+          <t>2026-10-06 02:27:45</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15982,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:11</t>
+          <t>2026-10-06 02:27:45</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16043,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:11</t>
+          <t>2026-10-06 02:27:45</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16104,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:11</t>
+          <t>2026-10-06 02:27:45</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:11</t>
+          <t>2026-10-06 02:27:45</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16226,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16287,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16318,7 +16348,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16379,7 +16409,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16440,7 +16470,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16501,7 +16531,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16562,7 +16592,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16623,7 +16653,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16684,7 +16714,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16745,7 +16775,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16806,7 +16836,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16867,7 +16897,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16928,7 +16958,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16989,7 +17019,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17050,7 +17080,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:18</t>
+          <t>2026-10-06 02:27:50</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17111,7 +17141,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17172,7 +17202,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17233,7 +17263,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17294,7 +17324,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17355,7 +17385,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17416,7 +17446,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17477,7 +17507,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17538,7 +17568,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17599,7 +17629,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17660,7 +17690,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17721,7 +17751,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17782,7 +17812,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17843,7 +17873,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17904,7 +17934,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17965,7 +17995,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:20</t>
+          <t>2026-10-06 02:27:52</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18026,7 +18056,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18087,7 +18117,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18148,7 +18178,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18209,7 +18239,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18270,7 +18300,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18331,7 +18361,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18392,7 +18422,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18453,7 +18483,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18514,7 +18544,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18575,7 +18605,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18636,7 +18666,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18697,7 +18727,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18758,7 +18788,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18819,7 +18849,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18880,7 +18910,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:21</t>
+          <t>2026-10-06 02:27:53</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18941,7 +18971,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:22</t>
+          <t>2026-10-06 02:27:54</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19002,7 +19032,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:22</t>
+          <t>2026-10-06 02:27:54</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19063,7 +19093,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:22</t>
+          <t>2026-10-06 02:27:54</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19124,7 +19154,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:22</t>
+          <t>2026-10-06 02:27:54</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19185,7 +19215,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:22</t>
+          <t>2026-10-06 02:27:54</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19246,7 +19276,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19307,7 +19337,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19368,7 +19398,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19429,7 +19459,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19490,7 +19520,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19551,7 +19581,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19612,7 +19642,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19673,7 +19703,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19734,7 +19764,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19795,7 +19825,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19856,7 +19886,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19917,7 +19947,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -19978,7 +20008,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20039,7 +20069,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20100,7 +20130,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20161,7 +20191,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20222,7 +20252,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20283,7 +20313,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20344,7 +20374,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20405,7 +20435,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20466,7 +20496,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20527,7 +20557,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20588,7 +20618,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20649,7 +20679,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20710,7 +20740,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20771,7 +20801,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20832,7 +20862,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20893,7 +20923,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20954,7 +20984,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21015,7 +21045,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21076,7 +21106,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21137,7 +21167,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21198,7 +21228,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21259,7 +21289,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21320,7 +21350,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21381,7 +21411,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21442,7 +21472,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21503,7 +21533,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21564,7 +21594,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21625,7 +21655,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21686,7 +21716,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21747,7 +21777,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21808,7 +21838,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:37</t>
+          <t>2026-10-06 02:28:07</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21871,7 +21901,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:37</t>
+          <t>2026-10-06 02:28:07</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21934,7 +21964,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:37</t>
+          <t>2026-10-06 02:28:07</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -21997,7 +22027,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22060,7 +22090,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22123,7 +22153,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22186,7 +22216,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22249,7 +22279,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22312,7 +22342,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:39</t>
+          <t>2026-10-06 02:28:09</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22375,7 +22405,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22438,7 +22468,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22501,7 +22531,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22564,7 +22594,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22627,7 +22657,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22690,7 +22720,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:40</t>
+          <t>2026-10-06 02:28:10</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22753,7 +22783,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22814,7 +22844,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -22875,7 +22905,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -22936,7 +22966,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -22997,7 +23027,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -23058,7 +23088,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -23119,7 +23149,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -23180,7 +23210,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -23241,7 +23271,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23302,7 +23332,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23363,7 +23393,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -23424,7 +23454,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -23485,7 +23515,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -23546,7 +23576,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23607,7 +23637,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:48</t>
+          <t>2026-10-06 02:28:17</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -23668,7 +23698,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -23729,7 +23759,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -23790,7 +23820,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -23851,7 +23881,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -23912,7 +23942,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -23973,7 +24003,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -24034,7 +24064,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -24095,7 +24125,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -24156,7 +24186,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -24217,7 +24247,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -24278,7 +24308,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -24339,7 +24369,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -24400,7 +24430,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -24461,7 +24491,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -24522,7 +24552,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:49</t>
+          <t>2026-10-06 02:28:18</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24583,7 +24613,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -24644,7 +24674,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -24705,7 +24735,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -24766,7 +24796,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -24827,7 +24857,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -24888,7 +24918,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -24949,7 +24979,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -25010,7 +25040,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -25071,7 +25101,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -25132,7 +25162,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -25193,7 +25223,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -25254,7 +25284,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -25315,7 +25345,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -25376,7 +25406,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25437,7 +25467,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:50</t>
+          <t>2026-10-06 02:28:19</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -25498,7 +25528,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -25559,7 +25589,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -25620,7 +25650,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -25681,7 +25711,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -25742,7 +25772,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25803,7 +25833,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -25864,7 +25894,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -25925,7 +25955,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -25986,7 +26016,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -26047,7 +26077,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -26108,7 +26138,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -26169,7 +26199,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -26230,7 +26260,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -26291,7 +26321,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -26352,7 +26382,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -26413,7 +26443,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -26474,7 +26504,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -26535,7 +26565,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -26596,7 +26626,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -26657,7 +26687,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -26718,7 +26748,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -26779,7 +26809,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -26840,7 +26870,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -26901,7 +26931,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -26962,7 +26992,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -27023,7 +27053,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -27084,7 +27114,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -27145,7 +27175,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -27206,7 +27236,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -27267,7 +27297,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -27328,7 +27358,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -27389,7 +27419,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -27450,7 +27480,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -27511,7 +27541,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -27572,7 +27602,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -27633,7 +27663,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -27694,7 +27724,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -27755,7 +27785,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -27816,7 +27846,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -27877,7 +27907,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -27938,7 +27968,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -27999,7 +28029,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28060,7 +28090,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -28121,7 +28151,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -28182,7 +28212,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -28243,7 +28273,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:01</t>
+          <t>2026-10-06 02:28:30</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -28304,7 +28334,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:01</t>
+          <t>2026-10-06 02:28:30</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -28365,7 +28395,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:01</t>
+          <t>2026-10-06 02:28:30</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -28426,7 +28456,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:01</t>
+          <t>2026-10-06 02:28:30</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -28487,7 +28517,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:01</t>
+          <t>2026-10-06 02:28:30</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -28548,7 +28578,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -28609,7 +28639,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -28670,7 +28700,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -28731,7 +28761,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -28792,7 +28822,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -28853,7 +28883,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -28914,7 +28944,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -28975,7 +29005,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -29036,7 +29066,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -29097,7 +29127,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -29158,7 +29188,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -29219,7 +29249,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -29280,7 +29310,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -29341,7 +29371,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -29402,7 +29432,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -29463,7 +29493,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -29524,7 +29554,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -29585,7 +29615,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -29646,7 +29676,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -29707,7 +29737,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -29768,7 +29798,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -29829,7 +29859,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -29890,7 +29920,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -29951,7 +29981,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -30012,7 +30042,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -30073,7 +30103,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -30134,7 +30164,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -30195,7 +30225,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -30256,7 +30286,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -30317,7 +30347,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -30378,7 +30408,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -30439,7 +30469,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -30500,7 +30530,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -30561,7 +30591,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -30622,7 +30652,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -30683,7 +30713,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -30744,7 +30774,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -30805,7 +30835,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -30866,7 +30896,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -30927,7 +30957,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -30988,7 +31018,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -31049,7 +31079,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -31110,7 +31140,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -31171,7 +31201,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -31232,7 +31262,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -31293,7 +31323,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -31354,7 +31384,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -31415,7 +31445,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -31476,7 +31506,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -31537,7 +31567,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -31598,7 +31628,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -31659,7 +31689,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -31720,7 +31750,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -31781,7 +31811,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -31842,7 +31872,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -31903,7 +31933,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -31964,7 +31994,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -32025,7 +32055,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -32086,7 +32116,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -32147,7 +32177,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -32208,7 +32238,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -32269,7 +32299,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -32330,7 +32360,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -32391,7 +32421,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -32452,7 +32482,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -32513,7 +32543,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -32574,7 +32604,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -32635,7 +32665,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -32696,7 +32726,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -32757,7 +32787,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -32818,7 +32848,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -32879,7 +32909,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -32940,7 +32970,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -33001,7 +33031,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -33062,7 +33092,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -33123,7 +33153,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -33184,7 +33214,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -33245,7 +33275,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -33306,7 +33336,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -33367,7 +33397,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -33428,7 +33458,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -33489,7 +33519,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -33550,7 +33580,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -33611,7 +33641,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -33672,7 +33702,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -33733,7 +33763,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -33794,7 +33824,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -33855,7 +33885,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -33916,7 +33946,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -33977,7 +34007,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -34038,7 +34068,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -34099,7 +34129,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -34160,7 +34190,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -34221,7 +34251,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -34282,7 +34312,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -34343,7 +34373,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">

--- a/etf_holdings/2026-10-06_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-10-06_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:28</t>
+          <t>2026-10-06 23:58:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:28</t>
+          <t>2026-10-06 23:58:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:28</t>
+          <t>2026-10-06 23:58:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:28</t>
+          <t>2026-10-06 23:58:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:28</t>
+          <t>2026-10-06 23:58:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:36</t>
+          <t>2026-10-06 23:58:09</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:36</t>
+          <t>2026-10-06 23:58:09</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:36</t>
+          <t>2026-10-06 23:58:09</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:36</t>
+          <t>2026-10-06 23:58:09</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:36</t>
+          <t>2026-10-06 23:58:09</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:51</t>
+          <t>2026-10-06 23:58:24</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:52</t>
+          <t>2026-10-06 23:58:25</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:53</t>
+          <t>2026-10-06 23:58:26</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:54</t>
+          <t>2026-10-06 23:58:27</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:00</t>
+          <t>2026-10-06 23:58:34</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:02</t>
+          <t>2026-10-06 23:58:36</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:03</t>
+          <t>2026-10-06 23:58:37</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:04</t>
+          <t>2026-10-06 23:58:38</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:04</t>
+          <t>2026-10-06 23:58:38</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:04</t>
+          <t>2026-10-06 23:58:38</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:04</t>
+          <t>2026-10-06 23:58:38</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:04</t>
+          <t>2026-10-06 23:58:38</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:17</t>
+          <t>2026-10-06 23:58:51</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21962,7 +21962,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:17</t>
+          <t>2026-10-06 23:58:51</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:17</t>
+          <t>2026-10-06 23:58:51</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22088,7 +22088,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:17</t>
+          <t>2026-10-06 23:58:51</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22214,7 +22214,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22277,7 +22277,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22340,7 +22340,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22403,7 +22403,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22529,7 +22529,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:18</t>
+          <t>2026-10-06 23:58:53</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22592,7 +22592,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:20</t>
+          <t>2026-10-06 23:58:54</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22655,7 +22655,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:20</t>
+          <t>2026-10-06 23:58:54</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:20</t>
+          <t>2026-10-06 23:58:54</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22781,7 +22781,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:20</t>
+          <t>2026-10-06 23:58:54</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22844,7 +22844,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -22966,7 +22966,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -23088,7 +23088,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -23149,7 +23149,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -23454,7 +23454,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -23515,7 +23515,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23637,7 +23637,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -23698,7 +23698,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:30</t>
+          <t>2026-10-06 23:59:01</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -23759,7 +23759,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -23820,7 +23820,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -23881,7 +23881,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -23942,7 +23942,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -24125,7 +24125,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -24247,7 +24247,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -24308,7 +24308,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -24430,7 +24430,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -24491,7 +24491,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24613,7 +24613,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:31</t>
+          <t>2026-10-06 23:59:02</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -24735,7 +24735,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -24796,7 +24796,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -24857,7 +24857,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -24918,7 +24918,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -24979,7 +24979,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -25101,7 +25101,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -25162,7 +25162,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -25223,7 +25223,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -25345,7 +25345,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -25406,7 +25406,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25467,7 +25467,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:32</t>
+          <t>2026-10-06 23:59:03</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -25589,7 +25589,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -25650,7 +25650,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -25711,7 +25711,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25833,7 +25833,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -25894,7 +25894,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -25955,7 +25955,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -26016,7 +26016,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -26077,7 +26077,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -26138,7 +26138,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -26199,7 +26199,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -26260,7 +26260,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -26321,7 +26321,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -26382,7 +26382,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -26443,7 +26443,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -26504,7 +26504,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -26626,7 +26626,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -26687,7 +26687,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -26748,7 +26748,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -26809,7 +26809,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -26870,7 +26870,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -26931,7 +26931,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -26992,7 +26992,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -27053,7 +27053,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -27114,7 +27114,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -27175,7 +27175,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -27236,7 +27236,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -27358,7 +27358,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -27419,7 +27419,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -27480,7 +27480,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -27541,7 +27541,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -27602,7 +27602,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -27663,7 +27663,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -27724,7 +27724,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -27785,7 +27785,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -27907,7 +27907,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -27968,7 +27968,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -28029,7 +28029,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28090,7 +28090,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -28151,7 +28151,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -28212,7 +28212,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -28273,7 +28273,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -28334,7 +28334,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:43</t>
+          <t>2026-10-06 23:59:17</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -28395,7 +28395,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:43</t>
+          <t>2026-10-06 23:59:17</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -28456,7 +28456,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:43</t>
+          <t>2026-10-06 23:59:17</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:43</t>
+          <t>2026-10-06 23:59:17</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -28578,7 +28578,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:43</t>
+          <t>2026-10-06 23:59:17</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -28639,7 +28639,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -28700,7 +28700,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -28761,7 +28761,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -28883,7 +28883,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -28944,7 +28944,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -29005,7 +29005,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -29127,7 +29127,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -29249,7 +29249,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -29310,7 +29310,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -29371,7 +29371,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -29432,7 +29432,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -29493,7 +29493,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -29615,7 +29615,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -29676,7 +29676,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -29737,7 +29737,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -29798,7 +29798,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -29859,7 +29859,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -29920,7 +29920,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -30103,7 +30103,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -30164,7 +30164,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -30225,7 +30225,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -30286,7 +30286,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -30347,7 +30347,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -30408,7 +30408,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -30469,7 +30469,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -30530,7 +30530,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -30591,7 +30591,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -30652,7 +30652,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -30713,7 +30713,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -30774,7 +30774,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -30835,7 +30835,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -30896,7 +30896,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -30957,7 +30957,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -31018,7 +31018,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -31079,7 +31079,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -31140,7 +31140,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -31201,7 +31201,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -31262,7 +31262,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -31323,7 +31323,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -31384,7 +31384,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -31445,7 +31445,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -31506,7 +31506,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -31567,7 +31567,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -31628,7 +31628,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -31689,7 +31689,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -31750,7 +31750,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -31811,7 +31811,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -31872,7 +31872,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -31933,7 +31933,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -31994,7 +31994,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -32055,7 +32055,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -32116,7 +32116,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -32177,7 +32177,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -32299,7 +32299,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -32421,7 +32421,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -32482,7 +32482,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -32543,7 +32543,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -32604,7 +32604,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -32665,7 +32665,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -32726,7 +32726,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -32787,7 +32787,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -32848,7 +32848,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -32909,7 +32909,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -32970,7 +32970,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -33031,7 +33031,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -33092,7 +33092,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -33153,7 +33153,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -33214,7 +33214,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -33275,7 +33275,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -33336,7 +33336,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -33397,7 +33397,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -33458,7 +33458,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -33580,7 +33580,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -33641,7 +33641,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -33702,7 +33702,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -33763,7 +33763,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -33885,7 +33885,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -33946,7 +33946,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -34007,7 +34007,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -34068,7 +34068,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -34129,7 +34129,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -34190,7 +34190,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -34251,7 +34251,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -34312,7 +34312,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -34373,7 +34373,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -34434,7 +34434,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
